--- a/DataRepo/data/tests/study_doc_versions/study_v2.xlsx
+++ b/DataRepo/data/tests/study_doc_versions/study_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/example_data/small_multitracer_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/study_doc_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3A21B1-1A98-684D-AE15-236273053875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D45241B-8FCF-9D44-BE1C-D8CC122C1728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="500" windowWidth="33200" windowHeight="26920" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="14760" windowWidth="33200" windowHeight="12580" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Animals" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,19 @@
     <sheet name="Treatments" sheetId="3" r:id="rId3"/>
     <sheet name="Tissues" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -42,8 +53,17 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t>Unique identifier for the animal (mouse) the sample was collected from. MUST match the Animal ID in the Animal Table.
-	-Lance Parsons</t>
+          <t xml:space="preserve">Unique identifier for the animal (mouse) the sample was collected from. MUST match the Animal ID in the Animal Table.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Lance Parsons</t>
         </r>
       </text>
     </comment>
@@ -334,8 +354,17 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t>Short, unique identifier for an animal treatment protocol. Must match the values provided in the Animals table.
-	-Lance Parsons</t>
+          <t xml:space="preserve">Short, unique identifier for an animal treatment protocol. Must match the values provided in the Animals table.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Lance Parsons</t>
         </r>
       </text>
     </comment>
@@ -386,13 +415,67 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t>@mneinast@princeton.edu @matthewmcbride@princeton.edu - I believe I have seen datasets with both "BAT" and "iBAT", which I likely have erroneously merged. Should we add "bat_inquinal" or similar?
-_Assigned to Michael Neinast_
-	-Lance Parsons
-I think they should be merged as just BAT.  It's an example of how abbreviations can be terrible:  here iBAT means "interscapular BAT" even though the i in iWAT means something else
-	-Michael Neinast
-Thanks, that's exactly the type of thing to sort out. Should the description be updated to say "interscapular brown adipose tissue"? Or is that just a specific type we don't need to keep track of all the time?
-	-Lance Parsons</t>
+          <t xml:space="preserve">@mneinast@princeton.edu @matthewmcbride@princeton.edu - I believe I have seen datasets with both "BAT" and "iBAT", which I likely have erroneously merged. Should we add "bat_inquinal" or similar?
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">_Assigned to Michael Neinast_
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Lance Parsons
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">I think they should be merged as just BAT.  It's an example of how abbreviations can be terrible:  here iBAT means "interscapular BAT" even though the i in iWAT means something else
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Michael Neinast
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Thanks, that's exactly the type of thing to sort out. Should the description be updated to say "interscapular brown adipose tissue"? Or is that just a specific type we don't need to keep track of all the time?
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Lance Parsons</t>
         </r>
       </text>
     </comment>
@@ -401,7 +484,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
   <si>
     <t>Animal ID</t>
   </si>
@@ -550,9 +633,6 @@
     <t>Treatment Description</t>
   </si>
   <si>
-    <t>No treatment was applied to the animal.  Animal was maintained on normal diet (LabDiet #5053 "Maintenance"), housed at room temperature with a normal light cycle.</t>
-  </si>
-  <si>
     <t>TraceBase Tissue Name</t>
   </si>
   <si>
@@ -667,9 +747,6 @@
     <t>testicle</t>
   </si>
   <si>
-    <t>testical</t>
-  </si>
-  <si>
     <t>ovary</t>
   </si>
   <si>
@@ -677,9 +754,6 @@
   </si>
   <si>
     <t>tumor_nonspecific</t>
-  </si>
-  <si>
-    <t>nonspecified tumor - only use this if other information is unknown</t>
   </si>
   <si>
     <t>tumor_hct116</t>
@@ -704,6 +778,12 @@
   </si>
   <si>
     <t>xz1078_t</t>
+  </si>
+  <si>
+    <t>no manipulation besides what is already described in other fields</t>
+  </si>
+  <si>
+    <t>unspecified tumor - only use this if other information is unknown</t>
   </si>
 </sst>
 </file>
@@ -785,28 +865,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -893,9 +969,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -933,7 +1009,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1039,7 +1115,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1181,7 +1257,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1194,13 +1270,14 @@
   <cols>
     <col min="2" max="4" width="16.83203125" customWidth="1"/>
     <col min="5" max="5" width="19.5" customWidth="1"/>
-    <col min="6" max="6" width="106.83203125" customWidth="1"/>
+    <col min="6" max="6" width="104" customWidth="1"/>
     <col min="7" max="7" width="20.33203125" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
     <col min="12" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="13" width="60.1640625" customWidth="1"/>
     <col min="1022" max="1024" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1268,7 +1345,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H2">
         <v>6.0999999999999999E-2</v>
@@ -1309,7 +1386,7 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H3">
         <v>0.114</v>
@@ -5188,7 +5265,7 @@
     </row>
     <row r="2" spans="1:30" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B2" s="7">
         <v>44316</v>
@@ -5218,7 +5295,7 @@
     </row>
     <row r="3" spans="1:30" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B3" s="7">
         <v>44316</v>
@@ -5247,92 +5324,92 @@
       <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:30" ht="14" x14ac:dyDescent="0.15">
-      <c r="A4" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="10">
+      <c r="A4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9">
         <v>44154</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
     </row>
     <row r="5" spans="1:30" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="A5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="9">
         <v>44154</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
     </row>
     <row r="6" spans="1:30" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="6"/>
@@ -9804,7 +9881,7 @@
       <c r="C254" s="6"/>
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
-      <c r="F254" s="9"/>
+      <c r="F254" s="6"/>
       <c r="G254" s="6"/>
       <c r="H254" s="6"/>
       <c r="I254" s="6"/>
@@ -10430,14 +10507,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="144.83203125" customWidth="1"/>
+    <col min="2" max="2" width="54.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C1" s="5"/>
@@ -10466,11 +10543,11 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>49</v>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -10491,13 +10568,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="13"/>
+      <c r="D1" s="5"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
@@ -10522,296 +10599,296 @@
       <c r="Z1" s="5"/>
     </row>
     <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="11"/>
+    </row>
+    <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="15"/>
-    </row>
-    <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="D5" s="11"/>
+    </row>
+    <row r="6" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="D6" s="11"/>
+    </row>
+    <row r="7" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="15"/>
-    </row>
-    <row r="7" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="15"/>
-    </row>
-    <row r="8" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="15"/>
-    </row>
-    <row r="9" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="15"/>
-    </row>
-    <row r="10" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="15"/>
-    </row>
-    <row r="11" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="12" t="s">
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="15"/>
-    </row>
-    <row r="13" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:26" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:26" ht="14" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="15"/>
-    </row>
-    <row r="14" spans="1:26" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="15"/>
-    </row>
-    <row r="15" spans="1:26" ht="14" x14ac:dyDescent="0.15">
-      <c r="A15" s="12" t="s">
+      <c r="B15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="14" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="12" t="s">
+      <c r="B16" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A17" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="16" t="s">
+      <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="12" t="s">
+    </row>
+    <row r="18" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A18" s="12" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A18" s="16" t="s">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="12" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="12" t="s">
+    <row r="21" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="12" t="s">
+      <c r="B21" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="12" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A22" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="12" t="s">
+      <c r="B22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="12" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="12" t="s">
+      <c r="B23" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="16" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A24" s="12" t="s">
+      <c r="B24" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A25" s="12" t="s">
+      <c r="B25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="12" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A26" s="12" t="s">
+      <c r="B26" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="12" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A27" s="12" t="s">
+      <c r="B27" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B28" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A28" s="12" t="s">
+    <row r="29" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A29" s="12" t="s">
+      <c r="B29" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="12" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A30" s="12" t="s">
+      <c r="B30" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="12" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A31" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A31" s="12" t="s">
+      <c r="B31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="12" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A32" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A32" s="12" t="s">
+      <c r="B32" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B33" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A34" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A33" s="12" t="s">
+      <c r="B34" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A34" s="12" t="s">
+      <c r="B35" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A36" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A35" s="12" t="s">
+      <c r="B36" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="14" x14ac:dyDescent="0.15">
-      <c r="A36" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
